--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M08/run_3/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M08/run_3/CF_M08_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.9355</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7436</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.9655</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8358</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.982</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8475</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.8475</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_06', 'AU_08']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_36</t>
@@ -1233,7 +1245,6 @@
           <t>system service, data service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Authentication</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1390,13 +1396,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Email</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1472,13 +1474,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Analytics</t>
@@ -1502,13 +1502,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,13 +1552,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Error monitoring</t>
@@ -1584,13 +1580,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1636,13 +1630,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Payment processing</t>
@@ -1666,13 +1658,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1718,13 +1708,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Cloud storage</t>
@@ -1748,13 +1736,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1795,14 +1781,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -1821,14 +1804,11 @@
       <c r="P9" t="n">
         <v>66</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1869,14 +1849,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -1900,13 +1877,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1947,14 +1922,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Amazon EC2</t>
@@ -1978,13 +1950,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_AU01</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2030,13 +2000,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>React</t>
@@ -2060,13 +2028,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_AU06</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2112,13 +2078,11 @@
           <t>['AU_25', 'AU_43']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Brevo</t>
@@ -2142,13 +2106,11 @@
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M08_AU21</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2189,14 +2151,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -2220,13 +2179,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2267,14 +2224,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -2298,13 +2252,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M08_AU22</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2350,13 +2302,11 @@
           <t>['AU_23', 'AU_42']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Sentry</t>
@@ -2380,13 +2330,11 @@
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M08_AU19</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2432,13 +2380,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
@@ -2462,13 +2408,11 @@
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M08_AU08</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2514,13 +2458,11 @@
           <t>['AU_15', 'AU_38']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Google</t>
@@ -2544,13 +2486,11 @@
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M08_AU11</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2596,13 +2536,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>ORM</t>
@@ -2626,13 +2564,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2678,13 +2614,11 @@
           <t>['AU_17', 'AU_39']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2708,13 +2642,11 @@
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M08_AU13</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2760,13 +2692,11 @@
           <t>['AU_19', 'AU_40']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Stripe</t>
@@ -2790,13 +2720,11 @@
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M08_AU15</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2842,13 +2770,11 @@
           <t>['AU_35']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_34</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>HTTPS</t>
@@ -2867,14 +2793,11 @@
       <c r="P22" t="n">
         <v>43</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M08_AU23</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2915,14 +2838,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -2941,14 +2861,11 @@
       <c r="P23" t="n">
         <v>41</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2994,13 +2911,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Traefik</t>
@@ -3024,13 +2939,11 @@
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3071,14 +2984,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -3102,13 +3012,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3154,13 +3062,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Next.js</t>
@@ -3184,13 +3090,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M08_AU05</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3231,14 +3135,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -3257,14 +3158,11 @@
       <c r="P27" t="n">
         <v>66</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3310,13 +3208,11 @@
           <t>['AU_21', 'AU_41']</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Google Analytics</t>
@@ -3340,13 +3236,11 @@
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M08_AU17</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3387,14 +3281,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -3413,14 +3304,11 @@
       <c r="P29" t="n">
         <v>67</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3466,13 +3354,11 @@
           <t>['AU_13', 'AU_36', 'AU_37']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -3496,13 +3382,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3576,7 +3460,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Usuario: Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
@@ -3612,7 +3495,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Empresa: Una empresa es un tipo de usuario que puede ofrecer productos con sus respectivas rutas para que los donantes los entreguen, comenzando así a crear una cadena.</t>
@@ -3648,7 +3530,6 @@
           <t>Donor</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Donante: Un donante es un tipo de usuario que contribuye con productos a una empresa.</t>
@@ -3684,7 +3565,6 @@
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Next.js soporta varios métodos de estilización, incluyendo módulos CSS, Tailwind CSS y CSS-in-JS, ofreciendo flexibilidad en la gestión de estilos.</t>
@@ -3720,7 +3600,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>TypeScript es un lenguaje de programación fuertemente tipado que se basa en JavaScript y le brinda mejores herramientas a cualquier escala</t>
@@ -3756,7 +3635,6 @@
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>para desarrollar esta aplicación se ha hecho uso de la herramienta GitLab, la cual facilita el control de versiones, la colaboración en el proyecto y el despliegue en diversos entornos.</t>
@@ -3792,7 +3670,6 @@
           <t>Terraform</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Terraform es una herramienta de infraestructura como código que permite definir y gestionar la infraestructura de manera declarativa</t>
@@ -3828,7 +3705,6 @@
           <t>Vitest</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Para testear las funcionalidades principales de la aplicación, Vitest has sido utilizado como entorno de pruebas para la realización de tests unitarios</t>
@@ -3864,7 +3740,6 @@
           <t>Vite</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Vitest, una basada en Vite, ha demostrado ser especialmente adecuada para aplicaciones de JavaScript y TypeScript</t>
@@ -3900,7 +3775,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
@@ -3931,7 +3805,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>security service, system service</t>
@@ -3967,7 +3840,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>data service, orm</t>
@@ -3983,7 +3855,6 @@
           <t>CF_M08_AU24</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0.7562</v>
       </c>
@@ -3999,7 +3870,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>system service, authentication service</t>
@@ -4035,7 +3905,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>system service, cloud storage service</t>
@@ -4071,7 +3940,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>system service, payment processing service</t>
@@ -4107,7 +3975,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>system service, analytics service</t>
@@ -4143,7 +4010,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>system service, error monitoring service</t>
@@ -4179,7 +4045,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>system service, email service</t>
@@ -4271,7 +4136,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
@@ -4312,7 +4176,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
